--- a/ig/DM-FEVRIER-2026/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
+++ b/ig/DM-FEVRIER-2026/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="623">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251222120000</t>
+    <t>20260223120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T12:00:00+01:00</t>
+    <t>2026-02-23T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1825,6 +1825,54 @@
   </si>
   <si>
     <t>Permanence d'Accès aux Soins de Santé (PASS)</t>
+  </si>
+  <si>
+    <t>296</t>
+  </si>
+  <si>
+    <t>Groupe d’Entraide Mutuelle (GEM)</t>
+  </si>
+  <si>
+    <t>297</t>
+  </si>
+  <si>
+    <t>Centre ressource IntimAgir</t>
+  </si>
+  <si>
+    <t>298</t>
+  </si>
+  <si>
+    <t>Dispositif sanitaire dédié à la prise en charge des femmes victimes de violences (Maison des Femmes Santé)</t>
+  </si>
+  <si>
+    <t>299</t>
+  </si>
+  <si>
+    <t>Equipe de Diagnostic de Proximité – Autisme (PDAP, EDAP)</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>Equipe Mobile de Psychiatrie Périnatale</t>
+  </si>
+  <si>
+    <t>301</t>
+  </si>
+  <si>
+    <t>Equipe Mobile de Psychiatrie de l’Enfant et de l’Adolescent (EMPEA)</t>
+  </si>
+  <si>
+    <t>302</t>
+  </si>
+  <si>
+    <t>Unité d'urgences psychiatriques</t>
+  </si>
+  <si>
+    <t>303</t>
+  </si>
+  <si>
+    <t>Centre d’Accueil et de Crise (CAC)</t>
   </si>
   <si>
     <t/>
@@ -2095,7 +2143,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B291"/>
+  <dimension ref="A1:B299"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -4419,15 +4467,79 @@
         <v>604</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="B292" t="s" s="2">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="B293" t="s" s="2">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="B294" t="s" s="2">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="B295" t="s" s="2">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="B296" t="s" s="2">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="B297" t="s" s="2">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="B298" t="s" s="2">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="B299" t="s" s="2">
+        <v>622</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-FEVRIER-2026/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
+++ b/ig/DM-FEVRIER-2026/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="621">
   <si>
     <t>Property</t>
   </si>
@@ -1728,7 +1728,7 @@
     <t>279</t>
   </si>
   <si>
-    <t>Equipe mobile de psychiatrie de l'Enfant et de l'Adolescent</t>
+    <t>Equipe Mobile de Psychiatrie de l’Enfant et de l’Adolescent (EMPEA)</t>
   </si>
   <si>
     <t>280</t>
@@ -1860,16 +1860,10 @@
     <t>301</t>
   </si>
   <si>
-    <t>Equipe Mobile de Psychiatrie de l’Enfant et de l’Adolescent (EMPEA)</t>
+    <t>Unité d'urgences psychiatriques</t>
   </si>
   <si>
     <t>302</t>
-  </si>
-  <si>
-    <t>Unité d'urgences psychiatriques</t>
-  </si>
-  <si>
-    <t>303</t>
   </si>
   <si>
     <t>Centre d’Accueil et de Crise (CAC)</t>
@@ -2143,7 +2137,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B299"/>
+  <dimension ref="A1:B298"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -4523,23 +4517,15 @@
         <v>618</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B298" t="s" s="2">
         <v>620</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="B299" t="s" s="2">
-        <v>622</v>
       </c>
     </row>
   </sheetData>
